--- a/results/log_pv_cap/log_pv_cap_densities_adensity_tests.xlsx
+++ b/results/log_pv_cap/log_pv_cap_densities_adensity_tests.xlsx
@@ -451,27 +451,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83.81***</t>
+          <t>80.66***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>39.66***</t>
+          <t>42.95***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8596.62***</t>
+          <t>8351.38***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>77.50***</t>
+          <t>66.93***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>833.51***</t>
+          <t>706.77***</t>
         </is>
       </c>
     </row>
@@ -483,27 +483,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.81***</t>
+          <t>80.66***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11.18***</t>
+          <t>12.09***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7148.80***</t>
+          <t>6653.06***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.65***</t>
+          <t>17.21***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>833.51***</t>
+          <t>706.77***</t>
         </is>
       </c>
     </row>
@@ -515,27 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>83.81***</t>
+          <t>80.66***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10.44***</t>
+          <t>10.86***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7132.59***</t>
+          <t>6624.65***</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.12***</t>
+          <t>11.58***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>833.51***</t>
+          <t>706.77***</t>
         </is>
       </c>
     </row>
